--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -36436,13 +36436,13 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O197" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R197" t="n">
-        <v>0.2616566519919337</v>
+        <v>0.2523117715636503</v>
       </c>
       <c r="S197" t="inlineStr">
         <is>
@@ -36595,10 +36595,10 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O198" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="U198" t="inlineStr">
         <is>
@@ -38216,13 +38216,13 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O208" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R208" t="n">
-        <v>0.02325563908550455</v>
+        <v>0.0251936090092966</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
@@ -38322,12 +38322,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -38352,22 +38352,22 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N209" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="O209" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="R209" t="n">
-        <v>0.3305530637567811</v>
+        <v>0.3364156954182004</v>
       </c>
       <c r="S209" t="inlineStr">
         <is>
@@ -38376,7 +38376,7 @@
       </c>
       <c r="U209" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -38386,7 +38386,7 @@
       </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
@@ -38396,12 +38396,12 @@
       </c>
       <c r="AQ209" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS209" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AT209" t="n">
@@ -38409,47 +38409,47 @@
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -38481,12 +38481,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -38511,38 +38511,38 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N210" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="O210" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="U210" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="V210" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="W210" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X210" t="inlineStr">
         <is>
-          <t>Hepatitis B (unspecified)</t>
+          <t>Hepatit B</t>
         </is>
       </c>
       <c r="Y210" t="inlineStr">
@@ -38552,7 +38552,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -38567,7 +38567,7 @@
       </c>
       <c r="AC210" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD210" t="inlineStr">
@@ -38582,7 +38582,7 @@
       </c>
       <c r="AF210" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG210" t="inlineStr">
@@ -38602,17 +38602,17 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
         <is>
-          <t>Unspecified acquisition status; not combinable with newly acquired without an explicit rule.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
         </is>
       </c>
       <c r="AM210" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN210" t="b">
@@ -38620,7 +38620,7 @@
       </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
@@ -38630,12 +38630,12 @@
       </c>
       <c r="AQ210" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS210" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AT210" t="n">
@@ -38643,47 +38643,47 @@
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -38715,118 +38715,511 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N211" t="n">
+        <v>90</v>
+      </c>
+      <c r="O211" t="n">
+        <v>90</v>
+      </c>
+      <c r="R211" t="n">
+        <v>0.3305530637567811</v>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO211" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP211" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT211" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU211" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV211" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW211" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX211" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY211" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA211" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB211" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC211" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N212" t="n">
+        <v>90</v>
+      </c>
+      <c r="O212" t="n">
+        <v>90</v>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>Hepatitis B (unspecified)</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD212" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF212" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG212" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH212" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI212" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ212" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK212" t="inlineStr">
+        <is>
+          <t>Unspecified acquisition status; not combinable with newly acquired without an explicit rule.</t>
+        </is>
+      </c>
+      <c r="AM212" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN212" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO212" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP212" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ212" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT212" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU212" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV212" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW212" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX212" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY212" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA212" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB212" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC212" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr">
+      <c r="G213" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>D008</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>Hepatitis B</t>
-        </is>
-      </c>
-      <c r="J211" t="inlineStr">
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
         <is>
           <t>乙型肝炎</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
+      <c r="K213" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L211" t="inlineStr">
+      <c r="L213" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M211" t="inlineStr">
+      <c r="M213" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N211" t="n">
+      <c r="N213" t="n">
         <v>1</v>
       </c>
-      <c r="O211" t="n">
+      <c r="O213" t="n">
         <v>1</v>
       </c>
-      <c r="R211" t="n">
+      <c r="R213" t="n">
         <v>0.001937969923792046</v>
       </c>
-      <c r="S211" t="inlineStr">
+      <c r="S213" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO211" t="inlineStr">
+      <c r="AO213" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP211" t="inlineStr">
+      <c r="AP213" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR211" t="inlineStr">
+      <c r="AR213" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS211" t="inlineStr"/>
-      <c r="AT211" t="n">
+      <c r="AS213" t="inlineStr"/>
+      <c r="AT213" t="n">
         <v>0</v>
       </c>
-      <c r="AU211" t="inlineStr">
+      <c r="AU213" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV211" t="inlineStr">
+      <c r="AV213" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW211" t="inlineStr">
+      <c r="AW213" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX211" t="inlineStr">
+      <c r="AX213" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY211" t="inlineStr">
+      <c r="AY213" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ211" t="inlineStr">
+      <c r="AZ213" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA211" t="inlineStr">
+      <c r="BA213" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB211" t="inlineStr">
+      <c r="BB213" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC211" t="inlineStr">
+      <c r="BC213" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -38948,7 +39341,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10">
@@ -38958,7 +39351,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -38978,7 +39371,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13">
@@ -39010,7 +39403,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1184784</v>
+        <v>1184820</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -39147,13 +39147,13 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O213" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R213" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.009689849618960231</v>
       </c>
       <c r="S213" t="inlineStr">
         <is>
@@ -39403,7 +39403,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1184820</v>
+        <v>1184824</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -25294,7 +25294,7 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN134" t="b">
@@ -30748,13 +30748,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="O165" t="n">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="R165" t="n">
-        <v>1.656438130603425</v>
+        <v>1.652765318783906</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -30907,10 +30907,10 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="O166" t="n">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="U166" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN166" t="b">
@@ -36829,13 +36829,13 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>227</v>
+        <v>434</v>
       </c>
       <c r="O199" t="n">
-        <v>227</v>
+        <v>434</v>
       </c>
       <c r="R199" t="n">
-        <v>0.8337282830309923</v>
+        <v>1.594000329671589</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
@@ -36988,10 +36988,10 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>227</v>
+        <v>434</v>
       </c>
       <c r="O200" t="n">
-        <v>227</v>
+        <v>434</v>
       </c>
       <c r="U200" t="inlineStr">
         <is>
@@ -37080,7 +37080,7 @@
       </c>
       <c r="AM200" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN200" t="b">
@@ -38177,12 +38177,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -38216,81 +38216,98 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>13</v>
+        <v>123628</v>
       </c>
       <c r="O208" t="n">
-        <v>13</v>
+        <v>123628</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>31</v>
       </c>
       <c r="R208" t="n">
-        <v>0.0251936090092966</v>
+        <v>8.749859669900234</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR208" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS208" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ208" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr">
+        <is>
+          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
+        </is>
+      </c>
       <c r="AT208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -38317,17 +38334,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -38361,22 +38378,39 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>36</v>
+        <v>123628</v>
       </c>
       <c r="O209" t="n">
-        <v>36</v>
-      </c>
-      <c r="R209" t="n">
-        <v>0.3364156954182004</v>
-      </c>
-      <c r="S209" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>123628</v>
       </c>
       <c r="U209" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>SRC_CN_CDC</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -38384,9 +38418,67 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>country:CN:national</t>
+        </is>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>China CDC hepatitis B series without a source-reported acute/chronic course split.</t>
+        </is>
+      </c>
+      <c r="AM209" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN209" t="b">
+        <v>1</v>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
@@ -38396,12 +38488,12 @@
       </c>
       <c r="AQ209" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS209" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="AT209" t="n">
@@ -38409,47 +38501,47 @@
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -38476,17 +38568,17 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -38520,170 +38612,81 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="O210" t="n">
-        <v>36</v>
-      </c>
-      <c r="U210" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
-        </is>
-      </c>
-      <c r="V210" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
-        </is>
-      </c>
-      <c r="W210" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X210" t="inlineStr">
-        <is>
-          <t>Hepatit B</t>
-        </is>
-      </c>
-      <c r="Y210" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z210" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA210" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB210" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD210" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE210" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF210" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG210" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH210" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI210" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ210" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK210" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
-        </is>
-      </c>
-      <c r="AM210" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN210" t="b">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="R210" t="n">
+        <v>0.0251936090092966</v>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ210" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS210" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR210" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr"/>
       <c r="AT210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -38715,12 +38718,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -38745,22 +38748,22 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N211" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="O211" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="R211" t="n">
-        <v>0.3305530637567811</v>
+        <v>0.3364156954182004</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
@@ -38769,7 +38772,7 @@
       </c>
       <c r="U211" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -38779,7 +38782,7 @@
       </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
@@ -38789,12 +38792,12 @@
       </c>
       <c r="AQ211" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS211" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AT211" t="n">
@@ -38802,47 +38805,47 @@
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -38874,12 +38877,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -38904,38 +38907,38 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N212" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="O212" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="U212" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="V212" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="W212" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X212" t="inlineStr">
         <is>
-          <t>Hepatitis B (unspecified)</t>
+          <t>Hepatit B</t>
         </is>
       </c>
       <c r="Y212" t="inlineStr">
@@ -38945,7 +38948,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -38960,7 +38963,7 @@
       </c>
       <c r="AC212" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD212" t="inlineStr">
@@ -38975,7 +38978,7 @@
       </c>
       <c r="AF212" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG212" t="inlineStr">
@@ -38995,17 +38998,17 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
         <is>
-          <t>Unspecified acquisition status; not combinable with newly acquired without an explicit rule.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
         </is>
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN212" t="b">
@@ -39013,7 +39016,7 @@
       </c>
       <c r="AO212" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP212" t="inlineStr">
@@ -39023,12 +39026,12 @@
       </c>
       <c r="AQ212" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS212" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AT212" t="n">
@@ -39036,47 +39039,47 @@
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -39108,118 +39111,511 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N213" t="n">
+        <v>90</v>
+      </c>
+      <c r="O213" t="n">
+        <v>90</v>
+      </c>
+      <c r="R213" t="n">
+        <v>0.3305530637567811</v>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO213" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP213" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ213" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU213" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV213" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW213" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX213" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY213" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA213" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB213" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC213" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N214" t="n">
+        <v>90</v>
+      </c>
+      <c r="O214" t="n">
+        <v>90</v>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>Hepatitis B (unspecified)</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD214" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF214" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG214" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ214" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK214" t="inlineStr">
+        <is>
+          <t>Unspecified acquisition status; not combinable with newly acquired without an explicit rule.</t>
+        </is>
+      </c>
+      <c r="AM214" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN214" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO214" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP214" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ214" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS214" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT214" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU214" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV214" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW214" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX214" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY214" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA214" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB214" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC214" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr">
+      <c r="G215" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>D008</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>Hepatitis B</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr">
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
         <is>
           <t>乙型肝炎</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
+      <c r="K215" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L213" t="inlineStr">
+      <c r="L215" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M213" t="inlineStr">
+      <c r="M215" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N213" t="n">
+      <c r="N215" t="n">
         <v>5</v>
       </c>
-      <c r="O213" t="n">
+      <c r="O215" t="n">
         <v>5</v>
       </c>
-      <c r="R213" t="n">
+      <c r="R215" t="n">
         <v>0.009689849618960231</v>
       </c>
-      <c r="S213" t="inlineStr">
+      <c r="S215" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO213" t="inlineStr">
+      <c r="AO215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP213" t="inlineStr">
+      <c r="AP215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR213" t="inlineStr">
+      <c r="AR215" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS213" t="inlineStr"/>
-      <c r="AT213" t="n">
+      <c r="AS215" t="inlineStr"/>
+      <c r="AT215" t="n">
         <v>0</v>
       </c>
-      <c r="AU213" t="inlineStr">
+      <c r="AU215" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV213" t="inlineStr">
+      <c r="AV215" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW213" t="inlineStr">
+      <c r="AW215" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX213" t="inlineStr">
+      <c r="AX215" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY213" t="inlineStr">
+      <c r="AY215" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ213" t="inlineStr">
+      <c r="AZ215" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA213" t="inlineStr">
+      <c r="BA215" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB213" t="inlineStr">
+      <c r="BB215" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC213" t="inlineStr">
+      <c r="BC215" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -39341,7 +39737,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10">
@@ -39351,7 +39747,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
@@ -39371,7 +39767,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13">
@@ -39403,7 +39799,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1184824</v>
+        <v>1308658</v>
       </c>
     </row>
     <row r="16">
@@ -39413,7 +39809,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>230</v>
+        <v>261</v>
       </c>
     </row>
     <row r="17">

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -30748,13 +30748,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O165" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="R165" t="n">
-        <v>1.652765318783906</v>
+        <v>1.656438130603425</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -30907,10 +30907,10 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O166" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="U166" t="inlineStr">
         <is>
@@ -38612,13 +38612,13 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O210" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R210" t="n">
-        <v>0.0251936090092966</v>
+        <v>0.02325563908550455</v>
       </c>
       <c r="S210" t="inlineStr">
         <is>
@@ -39543,13 +39543,13 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O215" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R215" t="n">
-        <v>0.009689849618960231</v>
+        <v>0.01356578946654432</v>
       </c>
       <c r="S215" t="inlineStr">
         <is>
@@ -39799,7 +39799,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1308658</v>
+        <v>1308660</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -36829,13 +36829,13 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="O199" t="n">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="R199" t="n">
-        <v>1.594000329671589</v>
+        <v>1.590327517852069</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
@@ -36988,10 +36988,10 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="O200" t="n">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="U200" t="inlineStr">
         <is>
@@ -39799,7 +39799,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1308660</v>
+        <v>1308659</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -38718,12 +38718,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -38757,13 +38757,13 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="O211" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="R211" t="n">
-        <v>0.3364156954182004</v>
+        <v>0.03782520932943658</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
       </c>
       <c r="U211" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -38797,7 +38797,7 @@
       </c>
       <c r="AS211" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT211" t="n">
@@ -38810,42 +38810,42 @@
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38877,12 +38877,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -38916,29 +38916,29 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="O212" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="U212" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="V212" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="W212" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X212" t="inlineStr">
         <is>
-          <t>Hepatit B</t>
+          <t>Hepatitis B</t>
         </is>
       </c>
       <c r="Y212" t="inlineStr">
@@ -38948,7 +38948,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -38963,7 +38963,7 @@
       </c>
       <c r="AC212" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD212" t="inlineStr">
@@ -38998,17 +38998,17 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+          <t>New Zealand PHF Science monthly hepatitis B notifications without a source-reported clinical-course split.</t>
         </is>
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN212" t="b">
@@ -39031,7 +39031,7 @@
       </c>
       <c r="AS212" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT212" t="n">
@@ -39044,42 +39044,42 @@
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39111,12 +39111,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -39141,22 +39141,22 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N213" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="O213" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="R213" t="n">
-        <v>0.3305530637567811</v>
+        <v>0.3364156954182004</v>
       </c>
       <c r="S213" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
       </c>
       <c r="U213" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -39175,7 +39175,7 @@
       </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP213" t="inlineStr">
@@ -39185,12 +39185,12 @@
       </c>
       <c r="AQ213" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS213" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AT213" t="n">
@@ -39198,47 +39198,47 @@
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -39270,12 +39270,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -39300,38 +39300,38 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N214" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="O214" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="U214" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="V214" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="W214" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X214" t="inlineStr">
         <is>
-          <t>Hepatitis B (unspecified)</t>
+          <t>Hepatit B</t>
         </is>
       </c>
       <c r="Y214" t="inlineStr">
@@ -39341,7 +39341,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -39356,7 +39356,7 @@
       </c>
       <c r="AC214" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD214" t="inlineStr">
@@ -39371,7 +39371,7 @@
       </c>
       <c r="AF214" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG214" t="inlineStr">
@@ -39391,17 +39391,17 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
         <is>
-          <t>Unspecified acquisition status; not combinable with newly acquired without an explicit rule.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
         </is>
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN214" t="b">
@@ -39409,7 +39409,7 @@
       </c>
       <c r="AO214" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP214" t="inlineStr">
@@ -39419,12 +39419,12 @@
       </c>
       <c r="AQ214" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS214" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AT214" t="n">
@@ -39432,47 +39432,47 @@
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV214" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA214" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB214" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC214" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -39504,118 +39504,511 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N215" t="n">
+        <v>90</v>
+      </c>
+      <c r="O215" t="n">
+        <v>90</v>
+      </c>
+      <c r="R215" t="n">
+        <v>0.3305530637567811</v>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO215" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP215" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ215" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU215" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV215" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW215" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX215" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY215" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA215" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB215" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC215" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N216" t="n">
+        <v>90</v>
+      </c>
+      <c r="O216" t="n">
+        <v>90</v>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t>Hepatitis B (unspecified)</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB216" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD216" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE216" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF216" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG216" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH216" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI216" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ216" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK216" t="inlineStr">
+        <is>
+          <t>Unspecified acquisition status; not combinable with newly acquired without an explicit rule.</t>
+        </is>
+      </c>
+      <c r="AM216" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN216" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO216" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP216" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ216" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS216" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT216" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU216" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV216" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW216" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX216" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY216" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA216" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB216" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC216" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr">
+      <c r="G217" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>D008</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>Hepatitis B</t>
-        </is>
-      </c>
-      <c r="J215" t="inlineStr">
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
         <is>
           <t>乙型肝炎</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
+      <c r="K217" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L215" t="inlineStr">
+      <c r="L217" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M215" t="inlineStr">
+      <c r="M217" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N215" t="n">
-        <v>7</v>
-      </c>
-      <c r="O215" t="n">
-        <v>7</v>
-      </c>
-      <c r="R215" t="n">
-        <v>0.01356578946654432</v>
-      </c>
-      <c r="S215" t="inlineStr">
+      <c r="N217" t="n">
+        <v>9</v>
+      </c>
+      <c r="O217" t="n">
+        <v>9</v>
+      </c>
+      <c r="R217" t="n">
+        <v>0.01744172931412841</v>
+      </c>
+      <c r="S217" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO215" t="inlineStr">
+      <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP215" t="inlineStr">
+      <c r="AP217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR215" t="inlineStr">
+      <c r="AR217" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS215" t="inlineStr"/>
-      <c r="AT215" t="n">
+      <c r="AS217" t="inlineStr"/>
+      <c r="AT217" t="n">
         <v>0</v>
       </c>
-      <c r="AU215" t="inlineStr">
+      <c r="AU217" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV215" t="inlineStr">
+      <c r="AV217" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW215" t="inlineStr">
+      <c r="AW217" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX215" t="inlineStr">
+      <c r="AX217" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY215" t="inlineStr">
+      <c r="AY217" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ215" t="inlineStr">
+      <c r="AZ217" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA215" t="inlineStr">
+      <c r="BA217" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB215" t="inlineStr">
+      <c r="BB217" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC215" t="inlineStr">
+      <c r="BC217" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -39737,7 +40130,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10">
@@ -39747,7 +40140,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
@@ -39767,7 +40160,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13">
@@ -39799,7 +40192,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1308659</v>
+        <v>1308663</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -39936,13 +39936,13 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O217" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="R217" t="n">
-        <v>0.01744172931412841</v>
+        <v>0.0251936090092966</v>
       </c>
       <c r="S217" t="inlineStr">
         <is>
@@ -40192,7 +40192,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1308663</v>
+        <v>1308667</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -30748,13 +30748,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="O165" t="n">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="R165" t="n">
-        <v>1.656438130603425</v>
+        <v>1.652765318783906</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -30907,10 +30907,10 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="O166" t="n">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="U166" t="inlineStr">
         <is>
@@ -39936,13 +39936,13 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O217" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R217" t="n">
-        <v>0.0251936090092966</v>
+        <v>0.02713157893308864</v>
       </c>
       <c r="S217" t="inlineStr">
         <is>

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -25284,7 +25284,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -30748,13 +30748,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O165" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="R165" t="n">
-        <v>1.652765318783906</v>
+        <v>1.656438130603425</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -30907,10 +30907,10 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O166" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="U166" t="inlineStr">
         <is>
@@ -30989,7 +30989,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -32521,7 +32521,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -36829,13 +36829,13 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O199" t="n">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="R199" t="n">
-        <v>1.590327517852069</v>
+        <v>1.586654706032549</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
@@ -36988,10 +36988,10 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O200" t="n">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="U200" t="inlineStr">
         <is>
@@ -37070,7 +37070,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
@@ -38460,7 +38460,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -38573,12 +38573,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -38612,13 +38612,13 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O210" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R210" t="n">
-        <v>0.02325563908550455</v>
+        <v>0</v>
       </c>
       <c r="S210" t="inlineStr">
         <is>
@@ -38651,42 +38651,42 @@
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -38718,12 +38718,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -38757,95 +38757,81 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O211" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="R211" t="n">
-        <v>0.03782520932943658</v>
+        <v>0.02325563908550455</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U211" t="inlineStr">
-        <is>
-          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA211" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ211" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS211" t="inlineStr">
-        <is>
-          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR211" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr"/>
       <c r="AT211" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -38872,7 +38858,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -38921,98 +38907,23 @@
       <c r="O212" t="n">
         <v>2</v>
       </c>
+      <c r="R212" t="n">
+        <v>0.03782520932943658</v>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U212" t="inlineStr">
         <is>
           <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
-      <c r="V212" t="inlineStr">
-        <is>
-          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W212" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X212" t="inlineStr">
-        <is>
-          <t>Hepatitis B</t>
-        </is>
-      </c>
-      <c r="Y212" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z212" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB212" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD212" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE212" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF212" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG212" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH212" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI212" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ212" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK212" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly hepatitis B notifications without a source-reported clinical-course split.</t>
-        </is>
-      </c>
-      <c r="AM212" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN212" t="b">
-        <v>1</v>
       </c>
       <c r="AO212" t="inlineStr">
         <is>
@@ -39106,17 +39017,17 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -39150,22 +39061,39 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="O213" t="n">
-        <v>36</v>
-      </c>
-      <c r="R213" t="n">
-        <v>0.3364156954182004</v>
-      </c>
-      <c r="S213" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="U213" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -39173,6 +39101,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD213" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF213" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG213" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH213" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ213" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK213" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly hepatitis B notifications without a source-reported clinical-course split.</t>
+        </is>
+      </c>
+      <c r="AM213" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN213" t="b">
+        <v>1</v>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -39190,7 +39176,7 @@
       </c>
       <c r="AS213" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT213" t="n">
@@ -39203,42 +39189,42 @@
       </c>
       <c r="AV213" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39265,7 +39251,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -39314,98 +39300,23 @@
       <c r="O214" t="n">
         <v>36</v>
       </c>
+      <c r="R214" t="n">
+        <v>0.3364156954182004</v>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U214" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
-      <c r="V214" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
-        </is>
-      </c>
-      <c r="W214" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X214" t="inlineStr">
-        <is>
-          <t>Hepatit B</t>
-        </is>
-      </c>
-      <c r="Y214" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z214" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA214" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB214" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD214" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE214" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF214" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG214" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH214" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI214" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ214" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK214" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
-        </is>
-      </c>
-      <c r="AM214" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN214" t="b">
-        <v>1</v>
       </c>
       <c r="AO214" t="inlineStr">
         <is>
@@ -39499,17 +39410,17 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -39534,31 +39445,48 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N215" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="O215" t="n">
-        <v>90</v>
-      </c>
-      <c r="R215" t="n">
-        <v>0.3305530637567811</v>
-      </c>
-      <c r="S215" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>36</v>
       </c>
       <c r="U215" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>Hepatit B</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -39566,9 +39494,67 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD215" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF215" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG215" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ215" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK215" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+        </is>
+      </c>
+      <c r="AM215" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN215" t="b">
+        <v>1</v>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP215" t="inlineStr">
@@ -39578,12 +39564,12 @@
       </c>
       <c r="AQ215" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS215" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AT215" t="n">
@@ -39591,47 +39577,47 @@
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA215" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -39658,7 +39644,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -39707,98 +39693,23 @@
       <c r="O216" t="n">
         <v>90</v>
       </c>
+      <c r="R216" t="n">
+        <v>0.3305530637567811</v>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U216" t="inlineStr">
         <is>
           <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
         </is>
       </c>
-      <c r="V216" t="inlineStr">
-        <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
-        </is>
-      </c>
-      <c r="W216" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X216" t="inlineStr">
-        <is>
-          <t>Hepatitis B (unspecified)</t>
-        </is>
-      </c>
-      <c r="Y216" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z216" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA216" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB216" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC216" t="inlineStr">
-        <is>
-          <t>country:AU:national</t>
-        </is>
-      </c>
-      <c r="AD216" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE216" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF216" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG216" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH216" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI216" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ216" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK216" t="inlineStr">
-        <is>
-          <t>Unspecified acquisition status; not combinable with newly acquired without an explicit rule.</t>
-        </is>
-      </c>
-      <c r="AM216" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN216" t="b">
-        <v>1</v>
       </c>
       <c r="AO216" t="inlineStr">
         <is>
@@ -39892,123 +39803,357 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N217" t="n">
+        <v>90</v>
+      </c>
+      <c r="O217" t="n">
+        <v>90</v>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>Hepatitis B (unspecified)</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD217" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF217" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG217" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI217" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ217" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK217" t="inlineStr">
+        <is>
+          <t>Unspecified acquisition status; not combinable with newly acquired without an explicit rule.</t>
+        </is>
+      </c>
+      <c r="AM217" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN217" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO217" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP217" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ217" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS217" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT217" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU217" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV217" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW217" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX217" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY217" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA217" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB217" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC217" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr">
+      <c r="F218" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr">
+      <c r="G218" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>D008</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>Hepatitis B</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr">
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
         <is>
           <t>乙型肝炎</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr">
+      <c r="K218" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L217" t="inlineStr">
+      <c r="L218" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M217" t="inlineStr">
+      <c r="M218" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N217" t="n">
-        <v>14</v>
-      </c>
-      <c r="O217" t="n">
-        <v>14</v>
-      </c>
-      <c r="R217" t="n">
-        <v>0.02713157893308864</v>
-      </c>
-      <c r="S217" t="inlineStr">
+      <c r="N218" t="n">
+        <v>15</v>
+      </c>
+      <c r="O218" t="n">
+        <v>15</v>
+      </c>
+      <c r="R218" t="n">
+        <v>0.02906954885688069</v>
+      </c>
+      <c r="S218" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO217" t="inlineStr">
+      <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP217" t="inlineStr">
+      <c r="AP218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR217" t="inlineStr">
+      <c r="AR218" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS217" t="inlineStr"/>
-      <c r="AT217" t="n">
+      <c r="AS218" t="inlineStr"/>
+      <c r="AT218" t="n">
         <v>0</v>
       </c>
-      <c r="AU217" t="inlineStr">
+      <c r="AU218" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV217" t="inlineStr">
+      <c r="AV218" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW217" t="inlineStr">
+      <c r="AW218" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX217" t="inlineStr">
+      <c r="AX218" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY217" t="inlineStr">
+      <c r="AY218" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ217" t="inlineStr">
+      <c r="AZ218" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA217" t="inlineStr">
+      <c r="BA218" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB217" t="inlineStr">
+      <c r="BB218" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC217" t="inlineStr">
+      <c r="BC218" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -40130,7 +40275,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10">
@@ -40140,7 +40285,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11">
@@ -40192,7 +40337,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1308667</v>
+        <v>1308668</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -33404,12 +33404,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -33443,10 +33443,10 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>22992</v>
+        <v>9210</v>
       </c>
       <c r="O181" t="n">
-        <v>22992</v>
+        <v>9210</v>
       </c>
       <c r="S181" t="inlineStr">
         <is>
@@ -33518,7 +33518,7 @@
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
@@ -33555,12 +33555,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -33594,10 +33594,10 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>22992</v>
+        <v>9210</v>
       </c>
       <c r="O182" t="n">
-        <v>22992</v>
+        <v>9210</v>
       </c>
       <c r="U182" t="inlineStr">
         <is>
@@ -33641,7 +33641,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>country:CN-GD:national</t>
+          <t>country:CN-FJ:national</t>
         </is>
       </c>
       <c r="AD182" t="inlineStr">
@@ -33752,7 +33752,7 @@
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
@@ -33789,12 +33789,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -33828,10 +33828,10 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>5904</v>
+        <v>22992</v>
       </c>
       <c r="O183" t="n">
-        <v>5904</v>
+        <v>22992</v>
       </c>
       <c r="S183" t="inlineStr">
         <is>
@@ -33903,7 +33903,7 @@
       </c>
       <c r="BB183" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC183" t="inlineStr">
@@ -33940,12 +33940,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -33979,10 +33979,10 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>5904</v>
+        <v>22992</v>
       </c>
       <c r="O184" t="n">
-        <v>5904</v>
+        <v>22992</v>
       </c>
       <c r="U184" t="inlineStr">
         <is>
@@ -34026,7 +34026,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>country:CN-HN:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD184" t="inlineStr">
@@ -34137,7 +34137,7 @@
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
@@ -34174,12 +34174,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -34213,10 +34213,10 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>2096</v>
+        <v>5904</v>
       </c>
       <c r="O185" t="n">
-        <v>2096</v>
+        <v>5904</v>
       </c>
       <c r="S185" t="inlineStr">
         <is>
@@ -34288,7 +34288,7 @@
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC185" t="inlineStr">
@@ -34325,12 +34325,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -34364,10 +34364,10 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>2096</v>
+        <v>5904</v>
       </c>
       <c r="O186" t="n">
-        <v>2096</v>
+        <v>5904</v>
       </c>
       <c r="U186" t="inlineStr">
         <is>
@@ -34411,7 +34411,7 @@
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>country:CN-JS:national</t>
+          <t>country:CN-HN:national</t>
         </is>
       </c>
       <c r="AD186" t="inlineStr">
@@ -34522,7 +34522,7 @@
       </c>
       <c r="BB186" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC186" t="inlineStr">
@@ -34559,12 +34559,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -34598,10 +34598,10 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>1506</v>
+        <v>2096</v>
       </c>
       <c r="O187" t="n">
-        <v>1506</v>
+        <v>2096</v>
       </c>
       <c r="S187" t="inlineStr">
         <is>
@@ -34673,7 +34673,7 @@
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
@@ -34710,12 +34710,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -34749,10 +34749,10 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>1506</v>
+        <v>2096</v>
       </c>
       <c r="O188" t="n">
-        <v>1506</v>
+        <v>2096</v>
       </c>
       <c r="U188" t="inlineStr">
         <is>
@@ -34796,7 +34796,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>country:CN-LN:national</t>
+          <t>country:CN-JS:national</t>
         </is>
       </c>
       <c r="AD188" t="inlineStr">
@@ -34907,7 +34907,7 @@
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC188" t="inlineStr">
@@ -34944,12 +34944,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -34983,10 +34983,10 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>21815</v>
+        <v>1506</v>
       </c>
       <c r="O189" t="n">
-        <v>21815</v>
+        <v>1506</v>
       </c>
       <c r="S189" t="inlineStr">
         <is>
@@ -35058,7 +35058,7 @@
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
@@ -35095,12 +35095,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -35134,10 +35134,10 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>21815</v>
+        <v>1506</v>
       </c>
       <c r="O190" t="n">
-        <v>21815</v>
+        <v>1506</v>
       </c>
       <c r="U190" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
       </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>country:CN-SC:national</t>
+          <t>country:CN-LN:national</t>
         </is>
       </c>
       <c r="AD190" t="inlineStr">
@@ -35292,7 +35292,7 @@
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
@@ -35329,12 +35329,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -35368,10 +35368,10 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>6</v>
+        <v>21815</v>
       </c>
       <c r="O191" t="n">
-        <v>6</v>
+        <v>21815</v>
       </c>
       <c r="S191" t="inlineStr">
         <is>
@@ -35443,7 +35443,7 @@
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
@@ -35480,12 +35480,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -35519,10 +35519,10 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>6</v>
+        <v>21815</v>
       </c>
       <c r="O192" t="n">
-        <v>6</v>
+        <v>21815</v>
       </c>
       <c r="U192" t="inlineStr">
         <is>
@@ -35566,7 +35566,7 @@
       </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>country:CN-SH:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD192" t="inlineStr">
@@ -35677,7 +35677,7 @@
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
@@ -35714,12 +35714,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -35753,81 +35753,87 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O193" t="n">
-        <v>0</v>
-      </c>
-      <c r="R193" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR193" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS193" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ193" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_HEPATITIS_B; SER_CN_PROV_REPORT_HEPATITIS_B</t>
+        </is>
+      </c>
       <c r="AT193" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -35854,17 +35860,17 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -35898,81 +35904,170 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="O194" t="n">
-        <v>22</v>
-      </c>
-      <c r="R194" t="n">
-        <v>0.04263533832342501</v>
-      </c>
-      <c r="S194" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>country:CN-SH:national</t>
+        </is>
+      </c>
+      <c r="AD194" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM194" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN194" t="b">
+        <v>1</v>
       </c>
       <c r="AO194" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR194" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS194" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ194" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_HEPATITIS_B; SER_CN_PROV_REPORT_HEPATITIS_B</t>
+        </is>
+      </c>
       <c r="AT194" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA194" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB194" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC194" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -36004,12 +36099,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -36043,95 +36138,81 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R195" t="n">
-        <v>0.01891260466471829</v>
+        <v>0</v>
       </c>
       <c r="S195" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U195" t="inlineStr">
-        <is>
-          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA195" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ195" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS195" t="inlineStr">
-        <is>
-          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR195" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr"/>
       <c r="AT195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -36158,17 +36239,17 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -36202,170 +36283,81 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="O196" t="n">
-        <v>1</v>
-      </c>
-      <c r="U196" t="inlineStr">
-        <is>
-          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V196" t="inlineStr">
-        <is>
-          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W196" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X196" t="inlineStr">
-        <is>
-          <t>Hepatitis B</t>
-        </is>
-      </c>
-      <c r="Y196" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA196" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD196" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE196" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF196" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG196" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH196" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI196" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ196" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK196" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly hepatitis B notifications without a source-reported clinical-course split.</t>
-        </is>
-      </c>
-      <c r="AM196" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN196" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="R196" t="n">
+        <v>0.04263533832342501</v>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO196" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ196" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS196" t="inlineStr">
-        <is>
-          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR196" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr"/>
       <c r="AT196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -36397,12 +36389,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -36436,13 +36428,13 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="O197" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="R197" t="n">
-        <v>0.2523117715636503</v>
+        <v>0.01891260466471829</v>
       </c>
       <c r="S197" t="inlineStr">
         <is>
@@ -36451,7 +36443,7 @@
       </c>
       <c r="U197" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -36476,7 +36468,7 @@
       </c>
       <c r="AS197" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT197" t="n">
@@ -36489,42 +36481,42 @@
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36556,12 +36548,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -36595,29 +36587,29 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="O198" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="U198" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="V198" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="W198" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X198" t="inlineStr">
         <is>
-          <t>Hepatit B</t>
+          <t>Hepatitis B</t>
         </is>
       </c>
       <c r="Y198" t="inlineStr">
@@ -36627,7 +36619,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -36642,7 +36634,7 @@
       </c>
       <c r="AC198" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD198" t="inlineStr">
@@ -36677,17 +36669,17 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+          <t>New Zealand PHF Science monthly hepatitis B notifications without a source-reported clinical-course split.</t>
         </is>
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN198" t="b">
@@ -36710,7 +36702,7 @@
       </c>
       <c r="AS198" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT198" t="n">
@@ -36723,42 +36715,42 @@
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36790,12 +36782,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -36820,22 +36812,22 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N199" t="n">
-        <v>432</v>
+        <v>27</v>
       </c>
       <c r="O199" t="n">
-        <v>432</v>
+        <v>27</v>
       </c>
       <c r="R199" t="n">
-        <v>1.586654706032549</v>
+        <v>0.2523117715636503</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
@@ -36844,7 +36836,7 @@
       </c>
       <c r="U199" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -36854,7 +36846,7 @@
       </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
@@ -36864,12 +36856,12 @@
       </c>
       <c r="AQ199" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS199" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AT199" t="n">
@@ -36877,47 +36869,47 @@
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -36949,12 +36941,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -36979,38 +36971,38 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N200" t="n">
-        <v>432</v>
+        <v>27</v>
       </c>
       <c r="O200" t="n">
-        <v>432</v>
+        <v>27</v>
       </c>
       <c r="U200" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="V200" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="W200" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X200" t="inlineStr">
         <is>
-          <t>Hepatitis B (unspecified)</t>
+          <t>Hepatit B</t>
         </is>
       </c>
       <c r="Y200" t="inlineStr">
@@ -37020,7 +37012,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -37035,7 +37027,7 @@
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD200" t="inlineStr">
@@ -37050,7 +37042,7 @@
       </c>
       <c r="AF200" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG200" t="inlineStr">
@@ -37070,17 +37062,17 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
         <is>
-          <t>Unspecified acquisition status; not combinable with newly acquired without an explicit rule.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
         </is>
       </c>
       <c r="AM200" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN200" t="b">
@@ -37088,7 +37080,7 @@
       </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
@@ -37098,12 +37090,12 @@
       </c>
       <c r="AQ200" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AT200" t="n">
@@ -37111,47 +37103,47 @@
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -37183,12 +37175,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -37222,38 +37214,55 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="O201" t="n">
-        <v>11</v>
+        <v>432</v>
+      </c>
+      <c r="R201" t="n">
+        <v>1.586654706032549</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR201" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS201" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ201" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
       <c r="AT201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
@@ -37263,12 +37272,12 @@
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
@@ -37283,12 +37292,12 @@
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
@@ -37320,17 +37329,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -37364,38 +37373,130 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>139</v>
+        <v>432</v>
       </c>
       <c r="O202" t="n">
-        <v>139</v>
-      </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>432</v>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>Hepatitis B (unspecified)</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD202" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>Unspecified acquisition status; not combinable with newly acquired without an explicit rule.</t>
+        </is>
+      </c>
+      <c r="AM202" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN202" t="b">
+        <v>1</v>
       </c>
       <c r="AO202" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR202" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS202" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ202" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
       <c r="AT202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
@@ -37405,12 +37506,12 @@
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
@@ -37425,12 +37526,12 @@
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
@@ -37467,12 +37568,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -37506,10 +37607,10 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="O203" t="n">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="S203" t="inlineStr">
         <is>
@@ -37547,7 +37648,7 @@
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
@@ -37567,7 +37668,7 @@
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
@@ -37609,12 +37710,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -37648,10 +37749,10 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>25</v>
+        <v>139</v>
       </c>
       <c r="O204" t="n">
-        <v>25</v>
+        <v>139</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
@@ -37689,7 +37790,7 @@
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
@@ -37709,7 +37810,7 @@
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
@@ -37751,12 +37852,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -37790,10 +37891,10 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="O205" t="n">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="S205" t="inlineStr">
         <is>
@@ -37831,7 +37932,7 @@
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
@@ -37851,7 +37952,7 @@
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
@@ -37893,12 +37994,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -37932,10 +38033,10 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>117</v>
+        <v>25</v>
       </c>
       <c r="O206" t="n">
-        <v>117</v>
+        <v>25</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
@@ -37973,7 +38074,7 @@
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
@@ -37993,7 +38094,7 @@
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
@@ -38035,12 +38136,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -38074,10 +38175,10 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="O207" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="S207" t="inlineStr">
         <is>
@@ -38115,7 +38216,7 @@
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
@@ -38135,7 +38236,7 @@
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
@@ -38177,12 +38278,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -38216,98 +38317,78 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>123628</v>
+        <v>117</v>
       </c>
       <c r="O208" t="n">
-        <v>123628</v>
-      </c>
-      <c r="Q208" t="n">
-        <v>31</v>
-      </c>
-      <c r="R208" t="n">
-        <v>8.749859669900234</v>
+        <v>117</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U208" t="inlineStr">
-        <is>
-          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
-        </is>
-      </c>
-      <c r="AA208" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ208" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS208" t="inlineStr">
-        <is>
-          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr"/>
       <c r="AT208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -38334,17 +38415,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -38378,170 +38459,78 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>123628</v>
+        <v>44</v>
       </c>
       <c r="O209" t="n">
-        <v>123628</v>
-      </c>
-      <c r="U209" t="inlineStr">
-        <is>
-          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
-        </is>
-      </c>
-      <c r="V209" t="inlineStr">
-        <is>
-          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
-        </is>
-      </c>
-      <c r="W209" t="inlineStr">
-        <is>
-          <t>SRC_CN_CDC</t>
-        </is>
-      </c>
-      <c r="X209" t="inlineStr">
-        <is>
-          <t>乙型肝炎</t>
-        </is>
-      </c>
-      <c r="Y209" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA209" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>country:CN:national</t>
-        </is>
-      </c>
-      <c r="AD209" t="inlineStr">
+        <v>44</v>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO209" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP209" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR209" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr"/>
+      <c r="AT209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU209" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV209" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE209" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF209" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG209" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH209" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI209" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ209" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK209" t="inlineStr">
-        <is>
-          <t>China CDC hepatitis B series without a source-reported acute/chronic course split.</t>
-        </is>
-      </c>
-      <c r="AM209" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN209" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO209" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP209" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ209" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS209" t="inlineStr">
-        <is>
-          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
-        </is>
-      </c>
-      <c r="AT209" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU209" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
-      <c r="AV209" t="inlineStr">
-        <is>
-          <t>cdc_weekly</t>
-        </is>
-      </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -38573,12 +38562,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -38612,81 +38601,98 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>0</v>
+        <v>123628</v>
       </c>
       <c r="O210" t="n">
-        <v>0</v>
+        <v>123628</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>31</v>
       </c>
       <c r="R210" t="n">
-        <v>0</v>
+        <v>8.749859669900234</v>
       </c>
       <c r="S210" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR210" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS210" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ210" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr">
+        <is>
+          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
+        </is>
+      </c>
       <c r="AT210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -38713,17 +38719,17 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -38757,81 +38763,170 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>12</v>
+        <v>123628</v>
       </c>
       <c r="O211" t="n">
-        <v>12</v>
-      </c>
-      <c r="R211" t="n">
-        <v>0.02325563908550455</v>
-      </c>
-      <c r="S211" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>123628</v>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>SRC_CN_CDC</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>country:CN:national</t>
+        </is>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>China CDC hepatitis B series without a source-reported acute/chronic course split.</t>
+        </is>
+      </c>
+      <c r="AM211" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN211" t="b">
+        <v>1</v>
       </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR211" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS211" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>SER_CN_HEPATITIS_B_UNSPECIFIED_COURSE</t>
+        </is>
+      </c>
       <c r="AT211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -38863,12 +38958,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -38902,95 +38997,87 @@
         </is>
       </c>
       <c r="N212" t="n">
+        <v>2434</v>
+      </c>
+      <c r="O212" t="n">
+        <v>2434</v>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO212" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP212" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ212" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_HEPATITIS_B; SER_CN_PROV_REPORT_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT212" t="n">
         <v>2</v>
       </c>
-      <c r="O212" t="n">
-        <v>2</v>
-      </c>
-      <c r="R212" t="n">
-        <v>0.03782520932943658</v>
-      </c>
-      <c r="S212" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U212" t="inlineStr">
-        <is>
-          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA212" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO212" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP212" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ212" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS212" t="inlineStr">
-        <is>
-          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT212" t="n">
-        <v>1</v>
-      </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -39022,12 +39109,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -39061,29 +39148,29 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>2</v>
+        <v>2434</v>
       </c>
       <c r="O213" t="n">
-        <v>2</v>
+        <v>2434</v>
       </c>
       <c r="U213" t="inlineStr">
         <is>
-          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_B</t>
         </is>
       </c>
       <c r="V213" t="inlineStr">
         <is>
-          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_B</t>
         </is>
       </c>
       <c r="W213" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X213" t="inlineStr">
         <is>
-          <t>Hepatitis B</t>
+          <t>乙型肝炎</t>
         </is>
       </c>
       <c r="Y213" t="inlineStr">
@@ -39093,7 +39180,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -39108,7 +39195,7 @@
       </c>
       <c r="AC213" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:CN-CQ:national</t>
         </is>
       </c>
       <c r="AD213" t="inlineStr">
@@ -39143,17 +39230,17 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly hepatitis B notifications without a source-reported clinical-course split.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -39166,7 +39253,7 @@
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ213" t="inlineStr">
@@ -39176,55 +39263,55 @@
       </c>
       <c r="AS213" t="inlineStr">
         <is>
-          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
+          <t>SER_CN_PROV_DC_HEPATITIS_B; SER_CN_PROV_REPORT_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AT213" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -39256,12 +39343,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -39295,22 +39382,14 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>36</v>
+        <v>22202</v>
       </c>
       <c r="O214" t="n">
-        <v>36</v>
-      </c>
-      <c r="R214" t="n">
-        <v>0.3364156954182004</v>
+        <v>22202</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U214" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -39325,7 +39404,7 @@
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ214" t="inlineStr">
@@ -39335,55 +39414,55 @@
       </c>
       <c r="AS214" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_CN_PROV_DC_HEPATITIS_B; SER_CN_PROV_REPORT_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AT214" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV214" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA214" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB214" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC214" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -39415,12 +39494,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -39454,29 +39533,29 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>36</v>
+        <v>22202</v>
       </c>
       <c r="O215" t="n">
-        <v>36</v>
+        <v>22202</v>
       </c>
       <c r="U215" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_B</t>
         </is>
       </c>
       <c r="V215" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_B</t>
         </is>
       </c>
       <c r="W215" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X215" t="inlineStr">
         <is>
-          <t>Hepatit B</t>
+          <t>乙型肝炎</t>
         </is>
       </c>
       <c r="Y215" t="inlineStr">
@@ -39486,7 +39565,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -39501,7 +39580,7 @@
       </c>
       <c r="AC215" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD215" t="inlineStr">
@@ -39536,17 +39615,17 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -39559,7 +39638,7 @@
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ215" t="inlineStr">
@@ -39569,55 +39648,55 @@
       </c>
       <c r="AS215" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+          <t>SER_CN_PROV_DC_HEPATITIS_B; SER_CN_PROV_REPORT_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AT215" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA215" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -39649,12 +39728,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -39679,31 +39758,23 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N216" t="n">
-        <v>90</v>
+        <v>5649</v>
       </c>
       <c r="O216" t="n">
-        <v>90</v>
-      </c>
-      <c r="R216" t="n">
-        <v>0.3305530637567811</v>
+        <v>5649</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U216" t="inlineStr">
-        <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -39713,70 +39784,70 @@
       </c>
       <c r="AO216" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ216" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS216" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_CN_PROV_DC_HEPATITIS_B; SER_CN_PROV_REPORT_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AT216" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA216" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB216" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC216" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -39808,12 +39879,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -39838,38 +39909,38 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N217" t="n">
-        <v>90</v>
+        <v>5649</v>
       </c>
       <c r="O217" t="n">
-        <v>90</v>
+        <v>5649</v>
       </c>
       <c r="U217" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_B</t>
         </is>
       </c>
       <c r="V217" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_B</t>
         </is>
       </c>
       <c r="W217" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X217" t="inlineStr">
         <is>
-          <t>Hepatitis B (unspecified)</t>
+          <t>乙型肝炎</t>
         </is>
       </c>
       <c r="Y217" t="inlineStr">
@@ -39879,7 +39950,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -39894,7 +39965,7 @@
       </c>
       <c r="AC217" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:CN-HN:national</t>
         </is>
       </c>
       <c r="AD217" t="inlineStr">
@@ -39909,7 +39980,7 @@
       </c>
       <c r="AF217" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG217" t="inlineStr">
@@ -39929,12 +40000,12 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
         <is>
-          <t>Unspecified acquisition status; not combinable with newly acquired without an explicit rule.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM217" t="inlineStr">
@@ -39947,70 +40018,70 @@
       </c>
       <c r="AO217" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ217" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS217" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+          <t>SER_CN_PROV_DC_HEPATITIS_B; SER_CN_PROV_REPORT_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AT217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA217" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -40042,118 +40113,3127 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N218" t="n">
+        <v>2009</v>
+      </c>
+      <c r="O218" t="n">
+        <v>2009</v>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO218" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP218" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ218" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS218" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_HEPATITIS_B; SER_CN_PROV_REPORT_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT218" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU218" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV218" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW218" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX218" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY218" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA218" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB218" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC218" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N219" t="n">
+        <v>2009</v>
+      </c>
+      <c r="O219" t="n">
+        <v>2009</v>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD219" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF219" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG219" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH219" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI219" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ219" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK219" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM219" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN219" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO219" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP219" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ219" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_HEPATITIS_B; SER_CN_PROV_REPORT_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT219" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU219" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV219" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW219" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX219" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY219" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA219" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB219" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC219" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>CN-LN</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Liaoning, China</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N220" t="n">
+        <v>1314</v>
+      </c>
+      <c r="O220" t="n">
+        <v>1314</v>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO220" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP220" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ220" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_HEPATITIS_B; SER_CN_PROV_REPORT_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT220" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU220" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV220" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW220" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX220" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY220" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA220" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB220" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+        </is>
+      </c>
+      <c r="BC220" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>CN-LN</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Liaoning, China</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N221" t="n">
+        <v>1314</v>
+      </c>
+      <c r="O221" t="n">
+        <v>1314</v>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>country:CN-LN:national</t>
+        </is>
+      </c>
+      <c r="AD221" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF221" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG221" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH221" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI221" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ221" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK221" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM221" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN221" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO221" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP221" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ221" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS221" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_HEPATITIS_B; SER_CN_PROV_REPORT_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT221" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU221" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV221" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW221" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX221" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA221" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB221" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+        </is>
+      </c>
+      <c r="BC221" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>CN-SC</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Sichuan, China</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N222" t="n">
+        <v>23346</v>
+      </c>
+      <c r="O222" t="n">
+        <v>23346</v>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO222" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP222" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ222" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS222" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_HEPATITIS_B; SER_CN_PROV_REPORT_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT222" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU222" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV222" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW222" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX222" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA222" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB222" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+        </is>
+      </c>
+      <c r="BC222" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>CN-SC</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Sichuan, China</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N223" t="n">
+        <v>23346</v>
+      </c>
+      <c r="O223" t="n">
+        <v>23346</v>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>country:CN-SC:national</t>
+        </is>
+      </c>
+      <c r="AD223" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF223" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG223" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH223" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI223" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ223" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK223" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM223" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN223" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO223" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP223" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ223" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_HEPATITIS_B; SER_CN_PROV_REPORT_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT223" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU223" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV223" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW223" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX223" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY223" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA223" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB223" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+        </is>
+      </c>
+      <c r="BC223" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N224" t="n">
+        <v>8</v>
+      </c>
+      <c r="O224" t="n">
+        <v>8</v>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO224" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP224" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ224" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS224" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_HEPATITIS_B; SER_CN_PROV_REPORT_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT224" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU224" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV224" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW224" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX224" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY224" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA224" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB224" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC224" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N225" t="n">
+        <v>8</v>
+      </c>
+      <c r="O225" t="n">
+        <v>8</v>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB225" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>country:CN-SH:national</t>
+        </is>
+      </c>
+      <c r="AD225" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF225" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG225" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH225" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI225" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ225" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK225" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM225" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN225" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO225" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP225" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ225" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_HEPATITIS_B; SER_CN_PROV_REPORT_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT225" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU225" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV225" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW225" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX225" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY225" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA225" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB225" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC225" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N226" t="n">
+        <v>0</v>
+      </c>
+      <c r="O226" t="n">
+        <v>0</v>
+      </c>
+      <c r="R226" t="n">
+        <v>0</v>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO226" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP226" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR226" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr"/>
+      <c r="AT226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU226" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV226" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW226" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX226" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY226" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA226" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB226" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC226" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr">
+      <c r="G227" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>D008</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>Hepatitis B</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr">
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
         <is>
           <t>乙型肝炎</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
+      <c r="K227" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L218" t="inlineStr">
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N227" t="n">
+        <v>12</v>
+      </c>
+      <c r="O227" t="n">
+        <v>12</v>
+      </c>
+      <c r="R227" t="n">
+        <v>0.02325563908550455</v>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO227" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP227" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR227" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr"/>
+      <c r="AT227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU227" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV227" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW227" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX227" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY227" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA227" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB227" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC227" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>NZ</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N228" t="n">
+        <v>2</v>
+      </c>
+      <c r="O228" t="n">
+        <v>2</v>
+      </c>
+      <c r="R228" t="n">
+        <v>0.03782520932943658</v>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO228" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP228" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ228" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr">
+        <is>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT228" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU228" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV228" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="AW228" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX228" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY228" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="BA228" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB228" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="BC228" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>NZ</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N229" t="n">
+        <v>2</v>
+      </c>
+      <c r="O229" t="n">
+        <v>2</v>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB229" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD229" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF229" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG229" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH229" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ229" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK229" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly hepatitis B notifications without a source-reported clinical-course split.</t>
+        </is>
+      </c>
+      <c r="AM229" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN229" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO229" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP229" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ229" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS229" t="inlineStr">
+        <is>
+          <t>SER_NZ_HEPATITIS_B_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT229" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU229" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV229" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="AW229" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX229" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY229" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="BA229" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB229" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="BC229" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N230" t="n">
+        <v>36</v>
+      </c>
+      <c r="O230" t="n">
+        <v>36</v>
+      </c>
+      <c r="R230" t="n">
+        <v>0.3364156954182004</v>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO230" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP230" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ230" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS230" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT230" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU230" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV230" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW230" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX230" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY230" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA230" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB230" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC230" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N231" t="n">
+        <v>36</v>
+      </c>
+      <c r="O231" t="n">
+        <v>36</v>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>Hepatit B</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD231" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE231" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF231" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG231" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH231" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI231" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ231" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK231" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+        </is>
+      </c>
+      <c r="AM231" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN231" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO231" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP231" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ231" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT231" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU231" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV231" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW231" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX231" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY231" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA231" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB231" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC231" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M218" t="inlineStr">
+      <c r="M232" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N218" t="n">
+      <c r="N232" t="n">
+        <v>90</v>
+      </c>
+      <c r="O232" t="n">
+        <v>90</v>
+      </c>
+      <c r="R232" t="n">
+        <v>0.3305530637567811</v>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO232" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP232" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ232" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT232" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU232" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV232" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW232" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX232" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY232" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA232" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB232" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC232" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N233" t="n">
+        <v>90</v>
+      </c>
+      <c r="O233" t="n">
+        <v>90</v>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>Hepatitis B (unspecified)</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB233" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD233" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE233" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF233" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG233" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH233" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI233" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ233" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK233" t="inlineStr">
+        <is>
+          <t>Unspecified acquisition status; not combinable with newly acquired without an explicit rule.</t>
+        </is>
+      </c>
+      <c r="AM233" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN233" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO233" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP233" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ233" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_B_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT233" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU233" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV233" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW233" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX233" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY233" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA233" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB233" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC233" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N234" t="n">
         <v>15</v>
       </c>
-      <c r="O218" t="n">
+      <c r="O234" t="n">
         <v>15</v>
       </c>
-      <c r="R218" t="n">
+      <c r="R234" t="n">
         <v>0.02906954885688069</v>
       </c>
-      <c r="S218" t="inlineStr">
+      <c r="S234" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO218" t="inlineStr">
+      <c r="AO234" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP218" t="inlineStr">
+      <c r="AP234" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR218" t="inlineStr">
+      <c r="AR234" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS218" t="inlineStr"/>
-      <c r="AT218" t="n">
+      <c r="AS234" t="inlineStr"/>
+      <c r="AT234" t="n">
         <v>0</v>
       </c>
-      <c r="AU218" t="inlineStr">
+      <c r="AU234" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV218" t="inlineStr">
+      <c r="AV234" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW218" t="inlineStr">
+      <c r="AW234" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX218" t="inlineStr">
+      <c r="AX234" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY218" t="inlineStr">
+      <c r="AY234" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ218" t="inlineStr">
+      <c r="AZ234" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA218" t="inlineStr">
+      <c r="BA234" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB218" t="inlineStr">
+      <c r="BB234" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC218" t="inlineStr">
+      <c r="BC234" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -40275,7 +43355,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>136</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10">
@@ -40285,7 +43365,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>217</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -40305,7 +43385,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13">
@@ -40337,7 +43417,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1308668</v>
+        <v>1374840</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -37214,13 +37214,13 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="O201" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="R201" t="n">
-        <v>1.586654706032549</v>
+        <v>1.594000329671589</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
@@ -37373,10 +37373,10 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="O202" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="U202" t="inlineStr">
         <is>
@@ -42768,13 +42768,13 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>90</v>
+        <v>414</v>
       </c>
       <c r="O232" t="n">
-        <v>90</v>
+        <v>414</v>
       </c>
       <c r="R232" t="n">
-        <v>0.3305530637567811</v>
+        <v>1.520544093281193</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
@@ -42927,10 +42927,10 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>90</v>
+        <v>414</v>
       </c>
       <c r="O233" t="n">
-        <v>90</v>
+        <v>414</v>
       </c>
       <c r="U233" t="inlineStr">
         <is>
@@ -43161,13 +43161,13 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O234" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R234" t="n">
-        <v>0.02906954885688069</v>
+        <v>0.03100751878067274</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
@@ -43234,6 +43234,151 @@
         </is>
       </c>
       <c r="BC234" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N235" t="n">
+        <v>0</v>
+      </c>
+      <c r="O235" t="n">
+        <v>0</v>
+      </c>
+      <c r="R235" t="n">
+        <v>0</v>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO235" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP235" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR235" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr"/>
+      <c r="AT235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU235" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV235" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW235" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX235" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY235" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA235" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB235" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC235" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -43272,7 +43417,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -43355,7 +43500,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10">
@@ -43365,7 +43510,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -43417,7 +43562,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1374840</v>
+        <v>1375167</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -37214,13 +37214,13 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="O201" t="n">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="R201" t="n">
-        <v>1.594000329671589</v>
+        <v>1.590327517852069</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
@@ -37373,10 +37373,10 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="O202" t="n">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="U202" t="inlineStr">
         <is>
@@ -42768,13 +42768,13 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="O232" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="R232" t="n">
-        <v>1.520544093281193</v>
+        <v>1.527889716920233</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
@@ -42927,10 +42927,10 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="O233" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="U233" t="inlineStr">
         <is>
@@ -43562,7 +43562,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1375167</v>
+        <v>1375168</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -66875,13 +66875,13 @@
         </is>
       </c>
       <c r="N350" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O350" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R350" t="n">
-        <v>0.03294548870446478</v>
+        <v>0.03488345862825683</v>
       </c>
       <c r="S350" t="inlineStr">
         <is>
@@ -67020,13 +67020,13 @@
         </is>
       </c>
       <c r="N351" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O351" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R351" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S351" t="inlineStr">
         <is>
@@ -67276,7 +67276,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1377849</v>
+        <v>1377851</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -63443,13 +63443,13 @@
         </is>
       </c>
       <c r="N332" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O332" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R332" t="n">
-        <v>0.3270708149899171</v>
+        <v>0.3177259345616337</v>
       </c>
       <c r="S332" t="inlineStr">
         <is>
@@ -63602,10 +63602,10 @@
         </is>
       </c>
       <c r="N333" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O333" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="U333" t="inlineStr">
         <is>
@@ -67280,13 +67280,13 @@
         </is>
       </c>
       <c r="N352" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O352" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R352" t="n">
-        <v>0.3831400975596171</v>
+        <v>0.3924849779879006</v>
       </c>
       <c r="S352" t="inlineStr">
         <is>
@@ -67439,10 +67439,10 @@
         </is>
       </c>
       <c r="N353" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O353" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U353" t="inlineStr">
         <is>

--- a/diseases/d008/2026-2029.xlsx
+++ b/diseases/d008/2026-2029.xlsx
@@ -16225,13 +16225,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O84" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R84" t="n">
-        <v>0.2803464128485004</v>
+        <v>0.271001532420217</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -16384,10 +16384,10 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O85" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U85" t="inlineStr">
         <is>
@@ -24012,13 +24012,13 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O125" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R125" t="n">
-        <v>0.3831400975596171</v>
+        <v>0.3737952171313338</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -24171,10 +24171,10 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O126" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="U126" t="inlineStr">
         <is>
@@ -31550,13 +31550,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="O165" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="R165" t="n">
-        <v>0.3924849779879006</v>
+        <v>0.3737952171313338</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -31709,10 +31709,10 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="O166" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="U166" t="inlineStr">
         <is>
@@ -39716,13 +39716,13 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="O208" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="R208" t="n">
-        <v>0.3924849779879006</v>
+        <v>0.3737952171313338</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
@@ -39875,10 +39875,10 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="O209" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="U209" t="inlineStr">
         <is>
@@ -47488,13 +47488,13 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="O249" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="R249" t="n">
-        <v>0.2336220107070837</v>
+        <v>0.2055873694222336</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
@@ -47647,10 +47647,10 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="O250" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="U250" t="inlineStr">
         <is>
@@ -67934,7 +67934,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1377992</v>
+        <v>1377983</v>
       </c>
     </row>
     <row r="16">
